--- a/cet4/result/49_职场女王_跨国集团的逆袭计划/49_职场女王_跨国集团的逆袭计划_学习版.xlsx
+++ b/cet4/result/49_职场女王_跨国集团的逆袭计划/49_职场女王_跨国集团的逆袭计划_学习版.xlsx
@@ -397,829 +397,661 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D46"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>porch</v>
       </c>
       <c r="B2" t="str">
-        <v>porch</v>
+        <v>/pɔːrtʃ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>门廊</v>
       </c>
-      <c r="D2" t="str">
-        <v>porch(门廊)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>host</v>
       </c>
       <c r="B3" t="str">
-        <v>host</v>
+        <v>/hoʊst/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>主持人</v>
       </c>
-      <c r="D3" t="str">
-        <v>host(主持人)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>Australia</v>
       </c>
       <c r="B4" t="str">
-        <v>Australia</v>
+        <v>/ɔːˈstreɪljə/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>澳大利亚</v>
       </c>
-      <c r="D4" t="str">
-        <v>Australia(澳大利亚)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>female</v>
       </c>
       <c r="B5" t="str">
-        <v>female</v>
+        <v>/ˈfiːmeɪl/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>女性的</v>
       </c>
-      <c r="D5" t="str">
-        <v>female(女性的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>turnip</v>
       </c>
       <c r="B6" t="str">
-        <v>turnip</v>
+        <v>/ˈtɜːrnɪp/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>萝卜</v>
       </c>
-      <c r="D6" t="str">
-        <v>turnip(萝卜)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>granddaughter</v>
       </c>
       <c r="B7" t="str">
-        <v>granddaughter</v>
+        <v>/ˈɡrændɔːtər/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>孙女</v>
       </c>
-      <c r="D7" t="str">
-        <v>granddaughter(孙女)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>introduction</v>
       </c>
       <c r="B8" t="str">
-        <v>introduction</v>
+        <v>/ˌɪntrəˈdʌkʃn/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>介绍</v>
       </c>
-      <c r="D8" t="str">
-        <v>introduction(介绍)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>trend</v>
       </c>
       <c r="B9" t="str">
-        <v>trend</v>
+        <v>/trend/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>趋势</v>
       </c>
-      <c r="D9" t="str">
-        <v>trend(趋势)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>factor</v>
       </c>
       <c r="B10" t="str">
-        <v>factor</v>
+        <v>/ˈfæktər/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>因素</v>
       </c>
-      <c r="D10" t="str">
-        <v>factor(因素)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>mathematics</v>
       </c>
       <c r="B11" t="str">
-        <v>mathematics</v>
+        <v>/ˌmæθəˈmætɪks/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>数学</v>
       </c>
-      <c r="D11" t="str">
-        <v>mathematics(数学)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>profit</v>
       </c>
       <c r="B12" t="str">
-        <v>profit</v>
+        <v>/ˈprɑːfɪt/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>利润</v>
       </c>
-      <c r="D12" t="str">
-        <v>profit(利润)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>lawn</v>
       </c>
       <c r="B13" t="str">
-        <v>lawn</v>
+        <v>/lɔːn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>草地</v>
       </c>
-      <c r="D13" t="str">
-        <v>lawn(草地)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>motor</v>
       </c>
       <c r="B14" t="str">
-        <v>motor</v>
+        <v>/ˈmoʊtər/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>发动机</v>
       </c>
-      <c r="D14" t="str">
-        <v>motor(发动机)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>specialist</v>
       </c>
       <c r="B15" t="str">
-        <v>porch</v>
+        <v>/ˈspeʃəlɪst/</v>
       </c>
       <c r="C15" t="str">
-        <v>门廊</v>
+        <v>n./adj.</v>
       </c>
       <c r="D15" t="str">
-        <v>porch(门廊)📢</v>
+        <v>专家</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>structural</v>
       </c>
       <c r="B16" t="str">
-        <v>specialist</v>
+        <v>/ˈstrʌktʃərəl/</v>
       </c>
       <c r="C16" t="str">
-        <v>专家</v>
+        <v>adj.</v>
       </c>
       <c r="D16" t="str">
-        <v>specialist(专家)📢</v>
+        <v>结构的</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>social</v>
       </c>
       <c r="B17" t="str">
-        <v>structural</v>
+        <v>/ˈsoʊʃl/</v>
       </c>
       <c r="C17" t="str">
-        <v>结构的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D17" t="str">
-        <v>structural(结构的)📢</v>
+        <v>社交</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>velvet</v>
       </c>
       <c r="B18" t="str">
-        <v>social</v>
+        <v>/ˈvelvɪt/</v>
       </c>
       <c r="C18" t="str">
-        <v>社交</v>
+        <v>n./adj.</v>
       </c>
       <c r="D18" t="str">
-        <v>social(社交)📢</v>
+        <v>天鹅绒</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>brisk</v>
       </c>
       <c r="B19" t="str">
-        <v>velvet</v>
+        <v>/brɪsk/</v>
       </c>
       <c r="C19" t="str">
-        <v>天鹅绒</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D19" t="str">
-        <v>velvet(天鹅绒)📢</v>
+        <v>活泼的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>westward</v>
       </c>
       <c r="B20" t="str">
-        <v>brisk</v>
+        <v>/ˈwestwərd/</v>
       </c>
       <c r="C20" t="str">
-        <v>活泼的</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D20" t="str">
-        <v>brisk(活泼的)📢</v>
+        <v>向西</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>lord</v>
       </c>
       <c r="B21" t="str">
-        <v>westward</v>
+        <v>/lɔːrd/</v>
       </c>
       <c r="C21" t="str">
-        <v>向西</v>
+        <v>n./vt./vi./int.</v>
       </c>
       <c r="D21" t="str">
-        <v>westward(向西)📢</v>
+        <v>主</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>poem</v>
       </c>
       <c r="B22" t="str">
-        <v>lord</v>
+        <v>/ˈpoʊəm/</v>
       </c>
       <c r="C22" t="str">
-        <v>主</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>lord(主)📢</v>
+        <v>诗</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>next</v>
       </c>
       <c r="B23" t="str">
-        <v>poem</v>
+        <v>/nekst/</v>
       </c>
       <c r="C23" t="str">
-        <v>诗</v>
+        <v>n./v./adj./adv./prep.</v>
       </c>
       <c r="D23" t="str">
-        <v>poem(诗)📢</v>
+        <v>下一个</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>dramatization</v>
       </c>
       <c r="B24" t="str">
-        <v>next</v>
+        <v>/ˌdræmətəˈzeɪʃn/</v>
       </c>
       <c r="C24" t="str">
-        <v>下一个</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>next(下一个)📢</v>
+        <v>编剧</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>respective</v>
       </c>
       <c r="B25" t="str">
-        <v>dramatization</v>
+        <v>/rɪˈspektɪv/</v>
       </c>
       <c r="C25" t="str">
-        <v>编剧</v>
+        <v>adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>dramatization(编剧)📢</v>
+        <v>各自的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>jacket</v>
       </c>
       <c r="B26" t="str">
-        <v>respective</v>
+        <v>/ˈdʒækɪt/</v>
       </c>
       <c r="C26" t="str">
-        <v>各自的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D26" t="str">
-        <v>respective(各自的)📢</v>
+        <v>夹克</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>black</v>
       </c>
       <c r="B27" t="str">
-        <v>jacket</v>
+        <v>/blæk/</v>
       </c>
       <c r="C27" t="str">
-        <v>夹克</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>jacket(夹克)📢</v>
+        <v>黑色</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>wing</v>
       </c>
       <c r="B28" t="str">
-        <v>black</v>
+        <v>/wɪŋ/</v>
       </c>
       <c r="C28" t="str">
-        <v>黑色</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>black(黑色)📢</v>
+        <v>翅膀</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>imagine</v>
       </c>
       <c r="B29" t="str">
-        <v>wing</v>
+        <v>/ɪˈmædʒɪn/</v>
       </c>
       <c r="C29" t="str">
-        <v>翅膀</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>wing(翅膀)📢</v>
+        <v>想象</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>postpone</v>
       </c>
       <c r="B30" t="str">
-        <v>imagine</v>
+        <v>/poʊˈspoʊn/</v>
       </c>
       <c r="C30" t="str">
-        <v>想象</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>imagine(想象)📢</v>
+        <v>推迟</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>uncertain</v>
       </c>
       <c r="B31" t="str">
-        <v>postpone</v>
+        <v>/ʌnˈsɜːrtn/</v>
       </c>
       <c r="C31" t="str">
-        <v>推迟</v>
+        <v>adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>postpone(推迟)📢</v>
+        <v>不确定的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>rapid</v>
       </c>
       <c r="B32" t="str">
-        <v>uncertain</v>
+        <v>/ˈræpɪd/</v>
       </c>
       <c r="C32" t="str">
-        <v>不确定的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>uncertain(不确定的)📢</v>
+        <v>迅速的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>increase</v>
       </c>
       <c r="B33" t="str">
-        <v>rapid</v>
+        <v>/ɪnˈkriːs; ˈɪnkriːs/</v>
       </c>
       <c r="C33" t="str">
-        <v>迅速的</v>
+        <v>n./v.</v>
       </c>
       <c r="D33" t="str">
-        <v>rapid(迅速的)📢</v>
+        <v>增加</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>rotten</v>
       </c>
       <c r="B34" t="str">
-        <v>trend</v>
+        <v>/ˈrɑːtn/</v>
       </c>
       <c r="C34" t="str">
-        <v>趋势</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D34" t="str">
-        <v>trend(趋势)📢</v>
+        <v>腐烂的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>toy</v>
       </c>
       <c r="B35" t="str">
-        <v>increase</v>
+        <v>/tɔɪ/</v>
       </c>
       <c r="C35" t="str">
-        <v>增加</v>
+        <v>n./vi./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>increase(增加)📢</v>
+        <v>玩具</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>soap</v>
       </c>
       <c r="B36" t="str">
-        <v>rotten</v>
+        <v>/soʊp/</v>
       </c>
       <c r="C36" t="str">
-        <v>腐烂的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>rotten(腐烂的)📢</v>
+        <v>肥皂</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>tale</v>
       </c>
       <c r="B37" t="str">
-        <v>toy</v>
+        <v>/teɪl/</v>
       </c>
       <c r="C37" t="str">
-        <v>玩具</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>toy(玩具)📢</v>
+        <v>故事</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>hair</v>
       </c>
       <c r="B38" t="str">
-        <v>soap</v>
+        <v>/her/</v>
       </c>
       <c r="C38" t="str">
-        <v>肥皂</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>soap(肥皂)📢</v>
+        <v>头发</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>certainly</v>
       </c>
       <c r="B39" t="str">
-        <v>turnip</v>
+        <v>/ˈsɜːrtnli/</v>
       </c>
       <c r="C39" t="str">
-        <v>萝卜</v>
+        <v>v./adv.</v>
       </c>
       <c r="D39" t="str">
-        <v>turnip(萝卜)📢</v>
+        <v>当然</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>sideways</v>
       </c>
       <c r="B40" t="str">
-        <v>tale</v>
+        <v>/ˈsaɪdweɪz/</v>
       </c>
       <c r="C40" t="str">
-        <v>故事</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D40" t="str">
-        <v>tale(故事)📢</v>
+        <v>间接的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>fancy</v>
       </c>
       <c r="B41" t="str">
-        <v>hair</v>
+        <v>/ˈfænsi/</v>
       </c>
       <c r="C41" t="str">
-        <v>头发</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>hair(头发)📢</v>
+        <v>奇特的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>journey</v>
       </c>
       <c r="B42" t="str">
-        <v>certainly</v>
+        <v>/ˈdʒɜːrni/</v>
       </c>
       <c r="C42" t="str">
-        <v>当然</v>
+        <v>n./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>certainly(当然)📢</v>
+        <v>旅行</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>advantage</v>
       </c>
       <c r="B43" t="str">
-        <v>profit</v>
+        <v>/ədˈvæntɪdʒ/</v>
       </c>
       <c r="C43" t="str">
-        <v>利润</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>profit(利润)📢</v>
+        <v>优势</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>emotional</v>
       </c>
       <c r="B44" t="str">
-        <v>sideways</v>
+        <v>/ɪˈmoʊʃənl/</v>
       </c>
       <c r="C44" t="str">
-        <v>间接的</v>
+        <v>adj.</v>
       </c>
       <c r="D44" t="str">
-        <v>sideways(间接的)📢</v>
+        <v>情绪的</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>who</v>
       </c>
       <c r="B45" t="str">
-        <v>fancy</v>
+        <v>/huː/</v>
       </c>
       <c r="C45" t="str">
-        <v>奇特的</v>
+        <v>n./pron.</v>
       </c>
       <c r="D45" t="str">
-        <v>fancy(奇特的)📢</v>
+        <v>谁</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>otherwise</v>
       </c>
       <c r="B46" t="str">
-        <v>Australia</v>
+        <v>/ˈʌðərwaɪz/</v>
       </c>
       <c r="C46" t="str">
-        <v>澳大利亚</v>
+        <v>v./adj./adv./conj.</v>
       </c>
       <c r="D46" t="str">
-        <v>Australia(澳大利亚)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>poem</v>
-      </c>
-      <c r="C47" t="str">
-        <v>诗</v>
-      </c>
-      <c r="D47" t="str">
-        <v>poem(诗)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>turnip</v>
-      </c>
-      <c r="C48" t="str">
-        <v>萝卜</v>
-      </c>
-      <c r="D48" t="str">
-        <v>turnip(萝卜)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>porch</v>
-      </c>
-      <c r="C49" t="str">
-        <v>门廊</v>
-      </c>
-      <c r="D49" t="str">
-        <v>porch(门廊)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>journey</v>
-      </c>
-      <c r="C50" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="D50" t="str">
-        <v>journey(旅行)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>advantage</v>
-      </c>
-      <c r="C51" t="str">
-        <v>优势</v>
-      </c>
-      <c r="D51" t="str">
-        <v>advantage(优势)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>trend</v>
-      </c>
-      <c r="C52" t="str">
-        <v>趋势</v>
-      </c>
-      <c r="D52" t="str">
-        <v>trend(趋势)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>social</v>
-      </c>
-      <c r="C53" t="str">
-        <v>社会</v>
-      </c>
-      <c r="D53" t="str">
-        <v>social(社会)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>emotional</v>
-      </c>
-      <c r="C54" t="str">
-        <v>情绪的</v>
-      </c>
-      <c r="D54" t="str">
-        <v>emotional(情绪的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>who</v>
-      </c>
-      <c r="C55" t="str">
-        <v>谁</v>
-      </c>
-      <c r="D55" t="str">
-        <v>who(谁)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>journey</v>
-      </c>
-      <c r="C56" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="D56" t="str">
-        <v>journey(旅行)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>tale</v>
-      </c>
-      <c r="C57" t="str">
-        <v>故事</v>
-      </c>
-      <c r="D57" t="str">
-        <v>tale(故事)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>otherwise</v>
-      </c>
-      <c r="C58" t="str">
         <v>否则</v>
-      </c>
-      <c r="D58" t="str">
-        <v>otherwise(否则)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D46"/>
   </ignoredErrors>
 </worksheet>
 </file>